--- a/output/pdf_financials_xlsx/RGI.xlsx
+++ b/output/pdf_financials_xlsx/RGI.xlsx
@@ -6980,13 +6980,13 @@
         <v>0.021665</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.021665</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.021665</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.021665</v>
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
@@ -10990,7 +10990,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RGI.xlsx
+++ b/output/pdf_financials_xlsx/RGI.xlsx
@@ -2354,25 +2354,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.219541</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.077001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.056444</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.367344</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.0176</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.060588</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.040021</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2510,25 +2510,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.219541</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.077001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.056444</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.367344</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.0176</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.060588</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.040021</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.076381</v>
+        <v>0.019937</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.462169</v>
+        <v>0.09482500000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.164175</v>
+        <v>0.146575</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
